--- a/data_extactor/batch_10_fa/trimmed/batch_0047_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0047_fa_trim.xlsx
@@ -508,12 +508,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | شنیدن فعال | درک مطلب | نظارت | نگارش | یادگیری فعال | علوم پایه | راهبردهای یادگیری</t>
+          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال | درک مطلب | نظارت | نگارش | یادگیری فعال | علوم | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | روانشناسی | زیست‌شناسی | درمان و مشاوره | آموزش و پرورش | خدمات مشتریان و خدمات فردی</t>
+          <t>پزشکی و دندان‌پزشکی | روان‌شناسی | زیست‌شناسی | درمان و مشاوره | آموزش و پرورش | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>متخصصان کایروپراکتیک | متخصصان مغز و اعصاب (نورولوژی) | کاردرمانگران | جراحان ارتوپدی (بزرگسالان) | کاردان‌های فیزیوتراپی | فیزیوتراپ‌ها | روان‌پزشکان</t>
+          <t>کایروپراکتورها / متخصصان درمان دستی | متخصصان مغز و اعصاب | کاردرمانگران | جراحان ارتوپدی، غیر از اطفال | کاردان‌های فیزیوتراپی | فیزیوتراپیست‌ها | روان‌پزشکان</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,12 +565,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | تفکر انتقادی | سخن گفتن | نگارش | نظارت | یادگیری فعال | علوم پایه | راهبردهای یادگیری | ریاضیات</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | سخن گفتن | نگارش | نظارت | یادگیری فعال | علوم | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | زیست‌شناسی | آموزش و پرورش | ایمنی و امنیت عمومی | حقوق و مقررات دولتی | درمان و مشاوره</t>
+          <t>پزشکی و دندان‌پزشکی | زیست‌شناسی | آموزش و پرورش | ایمنی و امنیت عمومی | قانون و دولت | درمان و مشاوره</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>اپیدمیولوژیست‌ها | پزشکان عمومی و طب خانواده | متخصصان بیماری‌های داخلی | متخصصان زنان و زایمان | پزشکان متخصص اطفال | دستیاران پزشک | پرستاران دارای پروانه</t>
+          <t>متخصصان همه‌گیرشناسی و اپیدمیولوژیست‌ها | پزشکان عمومی و خانواده | پزشکان متخصص بیماری‌های داخلی | متخصصان زنان و زایمان | متخصصان عمومی کودکان | دستیاران پزشک | پرستاران</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,12 +622,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | تفکر انتقادی | نظارت | سخن گفتن | یادگیری فعال | نگارش | راهبردهای یادگیری | علوم پایه</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | نظارت | سخن گفتن | یادگیری فعال | نگارش | راهبردهای یادگیری | علوم</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | زیست‌شناسی | زبان انگلیسی | خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | آموزش و پرورش</t>
+          <t>پزشکی و دندان‌پزشکی | زیست‌شناسی | زبان انگلیسی | خدمات مشتری و شخصی | مدیریت و اداره | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>مربیان بدنساز و مربیان توانبخشی ورزشی | متخصصان کایروپراکتیک | پزشکان عمومی و طب خانواده | جراحان ارتوپدی (بزرگسالان) | متخصصان طب فیزیکی و توانبخشی | فیزیوتراپ‌ها | متخصصان بیماری‌های پا (پودیاتریست‌ها)</t>
+          <t>مربیان و متخصصان سلامت و توان‌بخشی ورزشی | کایروپراکتورها / متخصصان درمان دستی | پزشکان عمومی و خانواده | جراحان ارتوپدی، غیر از اطفال | متخصصان طب فیزیکی و توانبخشی | فیزیوتراپیست‌ها | پزشکان متخصص پا و مچ پا</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | شنیدن فعال | یادگیری فعال | سخن گفتن | نگارش | نظارت | علوم پایه | راهبردهای یادگیری | ریاضیات</t>
+          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | یادگیری فعال | سخن گفتن | نگارش | نظارت | علوم | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | خدمات مشتریان و خدمات فردی | زیست‌شناسی | مدیریت و امور اداری | آموزش و پرورش | روانشناسی</t>
+          <t>پزشکی و دندان‌پزشکی | خدمات مشتری و شخصی | زیست‌شناسی | مدیریت و اداره | آموزش و پرورش | روان‌شناسی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | درک کتبی | دید نزدیک | استدلال استقرایی | بیان شفاهی | استدلال قیاسی | چابکی انگشتان</t>
+          <t>حساسیت به مسئله | درک کتبی | بینایی نزدیک | استدلال استقرایی | بیان شفاهی | استدلال قیاسی | مهارت انگشتان</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>متخصصان مغز و اعصاب (نورولوژی) | تکنسین‌های معاینات چشم‌پزشکی | تکنسین‌های ارشد اپتومتری و چشم‌شناسی | بینایی‌سنج‌ها (اپتومتریست‌ها) | جراحان ارتوپدی (بزرگسالان) | جراحان اطفال | پزشکان متخصص اطفال</t>
+          <t>متخصصان مغز و اعصاب | تکنسین‌های مراقبت‌های چشمی | کارشناسان فناوری پزشکی چشم | بینایی‌سنج‌ها (اپتومتریست‌ها) | جراحان ارتوپدی، غیر از اطفال | جراحان اطفال | متخصصان عمومی کودکان</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | تفکر انتقادی | سخن گفتن | علوم پایه | نظارت | یادگیری فعال | نگارش</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | سخن گفتن | علوم | نظارت | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | زیست‌شناسی | خدمات مشتریان و خدمات فردی | شیمی | روانشناسی | درمان و مشاوره</t>
+          <t>پزشکی و دندان‌پزشکی | زیست‌شناسی | خدمات مشتری و شخصی | شیمی | روان‌شناسی | درمان و مشاوره</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | حساسیت به مسئله | چابکی انگشتان | ثبات دست و بازو</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | حساسیت به مسئله | مهارت انگشتان | ثبات دست و بازو</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>متخصصان بیهوشی | متخصصان کایروپراکتیک | متخصصان طب اورژانس | جراحان اطفال | متخصصان طب فیزیکی و توانبخشی | متخصصان بیماری‌های پا (پودیاتریست‌ها) | متخصصان رادیولوژی</t>
+          <t>متخصصان بیهوشی | کایروپراکتورها / متخصصان درمان دستی | پزشکان طب اورژانس | جراحان اطفال | متخصصان طب فیزیکی و توانبخشی | پزشکان متخصص پا و مچ پا | متخصصان رادیولوژی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | تفکر انتقادی | سخن گفتن | علوم پایه | نظارت | یادگیری فعال | نگارش</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | سخن گفتن | علوم | نظارت | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | زیست‌شناسی | روانشناسی | خدمات مشتریان و خدمات فردی | شیمی | درمان و مشاوره</t>
+          <t>پزشکی و دندان‌پزشکی | زیست‌شناسی | روان‌شناسی | خدمات مشتری و شخصی | شیمی | درمان و مشاوره</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | حساسیت به مسئله | چابکی انگشتان | ثبات دست و بازو</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | حساسیت به مسئله | مهارت انگشتان | ثبات دست و بازو</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>متخصصان بیهوشی | متخصصان طب اورژانس | متخصصان زنان و زایمان | جراحان ارتوپدی (بزرگسالان) | پزشکان متخصص اطفال | دستیاران پزشک | متخصصان رادیولوژی</t>
+          <t>متخصصان بیهوشی | پزشکان طب اورژانس | متخصصان زنان و زایمان | جراحان ارتوپدی، غیر از اطفال | متخصصان عمومی کودکان | دستیاران پزشک | متخصصان رادیولوژی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | تفکر انتقادی | سخن گفتن | علوم پایه | نظارت | یادگیری فعال | نگارش</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | سخن گفتن | علوم | نظارت | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | زیست‌شناسی | شیمی | خدمات مشتریان و خدمات فردی | روانشناسی | مدیریت و امور اداری</t>
+          <t>پزشکی و دندان‌پزشکی | زیست‌شناسی | شیمی | خدمات مشتری و شخصی | روان‌شناسی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | حساسیت به مسئله | چابکی انگشتان | ثبات دست و بازو</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | حساسیت به مسئله | مهارت انگشتان | ثبات دست و بازو</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>جراحان ارتوپدی (بزرگسالان) | جراحان اطفال | جراحان دهان، فک و صورت | متخصصان بیهوشی | دستیاران جراحی | تکنسین‌های اتاق عمل | پرستاران بیهوشی</t>
+          <t>جراحان ارتوپدی، غیر از اطفال | جراحان اطفال | جراحان دهان، فک و صورت | متخصصان بیهوشی | دستیاران جراحی | تکنسین‌های اتاق عمل | پرستاران بیهوشی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی | سخن گفتن | نظارت | درک مطلب | نگارش | یادگیری فعال</t>
+          <t>گوش دادن فعال | تفکر انتقادی | سخن گفتن | نظارت | درک مطلب | نگارش | یادگیری فعال</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | پزشکی و دندانپزشکی | روانشناسی | زیست‌شناسی | درمان و مشاوره | مدیریت و امور اداری</t>
+          <t>خدمات مشتری و شخصی | پزشکی و دندان‌پزشکی | روان‌شناسی | زیست‌شناسی | درمان و مشاوره | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>دید نزدیک | درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | ثبات دست و بازو | چابکی انگشتان</t>
+          <t>بینایی نزدیک | درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | ثبات دست و بازو | مهارت انگشتان</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>متخصصان کایروپراکتیک | پزشکان عمومی و طب خانواده | ماساژدرمانگران | پزشکان طب سنتی و مکمل | متخصصان مغز و اعصاب (نورولوژی) | متخصصان طب فیزیکی و توانبخشی | فیزیوتراپ‌ها</t>
+          <t>کایروپراکتورها / متخصصان درمان دستی | پزشکان عمومی و خانواده | ماساژدرمانگران | پزشکان طب طبیعی و نتوپاتی | متخصصان مغز و اعصاب | متخصصان طب فیزیکی و توانبخشی | فیزیوتراپیست‌ها</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی | سخن گفتن | نگارش | نظارت | یادگیری فعال | درک مطلب</t>
+          <t>گوش دادن فعال | تفکر انتقادی | سخن گفتن | نگارش | نظارت | یادگیری فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | خدمات مشتریان و خدمات فردی</t>
+          <t>پزشکی و دندان‌پزشکی | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | چابکی انگشتان | دید نزدیک | حساسیت به مسئله | درک شفاهی | بیان شفاهی | چابکی دستی</t>
+          <t>ثبات دست و بازو | مهارت انگشتان | بینایی نزدیک | حساسیت به مسئله | درک شفاهی | بیان شفاهی | مهارت دستی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>دستیاران دندانپزشک | دندانپزشکان عمومی | جراحان دهان، فک و صورت | متخصصان ارتودنسی | متخصصان پروتزهای دندانی (پروستودنتیست‌ها) | دستیاران جراحی | تکنسین‌های اتاق عمل</t>
+          <t>دستیاران دندان‌پزشک | دندان‌پزشکان عمومی | جراحان دهان، فک و صورت | متخصصان ارتودنسی | متخصصان پروتزهای دندانی (پروستودنتیست‌ها) | دستیاران جراحی | تکنسین‌های اتاق عمل</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,12 +1021,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | تفکر انتقادی | سخن گفتن | علوم پایه | نظارت | یادگیری فعال | نگارش</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | سخن گفتن | علوم | نظارت | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | زیست‌شناسی | درمان و مشاوره | خدمات مشتریان و خدمات فردی | روانشناسی | آموزش و پرورش</t>
+          <t>پزشکی و دندان‌پزشکی | زیست‌شناسی | درمان و مشاوره | خدمات مشتری و شخصی | روان‌شناسی | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>متخصصان و کارشناسان طب سوزنی | پزشکان طب سنتی و مکمل | ارتوپتیست‌ها | متخصصان کایروپراکتیک | کارشناسان و متخصصان تغذیه و رژیم‌درمانی | متخصصان بیماری‌های پا (پودیاتریست‌ها) | سایر متخصصان درمان و توانبخشی</t>
+          <t>متخصصان و کارشناسان طب سوزنی | پزشکان طب طبیعی و نتوپاتی | ارتوپتیست‌ها / متخصصان ارتوپتیک | کایروپراکتورها / متخصصان درمان دستی | کارشناسان و متخصصان تغذیه و رژیم‌درمانی | پزشکان متخصص پا و مچ پا | سایر درمانگران</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
